--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados/FÉRIAS.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados/FÉRIAS.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe30ea445c4cf45e/Corporativo/I2A2/I2A2-Agentes Inteligentes com Redes Generativas/Dados Desafios/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{615BAD42-E0B0-45C1-92BD-BF6C1C3CFC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D59BDC2-2599-450C-A71A-109E17EDE969}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49EE956-542A-47DE-8E22-40B80152C19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{51FD5E32-E0AA-4576-973B-88CBD3E5DB56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51FD5E32-E0AA-4576-973B-88CBD3E5DB56}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$81</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -397,15 +403,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE483CA-FC21-4D49-9D12-BE057BED5155}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C81"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +423,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>32104</v>
       </c>
@@ -427,7 +434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>32761</v>
       </c>
@@ -438,7 +445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>30567</v>
       </c>
@@ -449,7 +456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>30502</v>
       </c>
@@ -460,7 +467,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>33998</v>
       </c>
@@ -471,7 +478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>30867</v>
       </c>
@@ -482,7 +489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>31237</v>
       </c>
@@ -493,7 +500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>32278</v>
       </c>
@@ -504,7 +511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>33808</v>
       </c>
@@ -515,7 +522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26910</v>
       </c>
@@ -526,7 +533,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>30206</v>
       </c>
@@ -537,7 +544,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>32216</v>
       </c>
@@ -548,7 +555,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>30570</v>
       </c>
@@ -559,7 +566,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>32589</v>
       </c>
@@ -570,7 +577,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>31740</v>
       </c>
@@ -581,7 +588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>33235</v>
       </c>
@@ -592,7 +599,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>34042</v>
       </c>
@@ -603,7 +610,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>33420</v>
       </c>
@@ -614,7 +621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>31190</v>
       </c>
@@ -625,7 +632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>31208</v>
       </c>
@@ -636,7 +643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>33715</v>
       </c>
@@ -647,7 +654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>30280</v>
       </c>
@@ -658,7 +665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>34444</v>
       </c>
@@ -669,7 +676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>29058</v>
       </c>
@@ -680,7 +687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>33628</v>
       </c>
@@ -691,7 +698,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>33795</v>
       </c>
@@ -702,7 +709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>33633</v>
       </c>
@@ -713,7 +720,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26463</v>
       </c>
@@ -724,7 +731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>31333</v>
       </c>
@@ -735,7 +742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>33132</v>
       </c>
@@ -746,7 +753,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>32473</v>
       </c>
@@ -757,7 +764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30140</v>
       </c>
@@ -768,7 +775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>34506</v>
       </c>
@@ -779,7 +786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32344</v>
       </c>
@@ -790,7 +797,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>30205</v>
       </c>
@@ -801,7 +808,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>30426</v>
       </c>
@@ -812,7 +819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>30281</v>
       </c>
@@ -823,7 +830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>32383</v>
       </c>
@@ -834,7 +841,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>33562</v>
       </c>
@@ -845,7 +852,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>33608</v>
       </c>
@@ -856,7 +863,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>34447</v>
       </c>
@@ -867,7 +874,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>34385</v>
       </c>
@@ -878,7 +885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>32209</v>
       </c>
@@ -889,7 +896,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>32229</v>
       </c>
@@ -900,7 +907,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>34499</v>
       </c>
@@ -911,7 +918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>33863</v>
       </c>
@@ -922,7 +929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>33776</v>
       </c>
@@ -933,7 +940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>33728</v>
       </c>
@@ -944,7 +951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>33712</v>
       </c>
@@ -955,7 +962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>30276</v>
       </c>
@@ -966,7 +973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>30249</v>
       </c>
@@ -977,7 +984,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>31061</v>
       </c>
@@ -988,7 +995,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>33114</v>
       </c>
@@ -999,7 +1006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>34311</v>
       </c>
@@ -1010,7 +1017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>32423</v>
       </c>
@@ -1021,7 +1028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>30623</v>
       </c>
@@ -1032,7 +1039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>34245</v>
       </c>
@@ -1043,7 +1050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>31840</v>
       </c>
@@ -1054,7 +1061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>31649</v>
       </c>
@@ -1065,7 +1072,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>34492</v>
       </c>
@@ -1076,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>30739</v>
       </c>
@@ -1087,7 +1094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>28927</v>
       </c>
@@ -1098,7 +1105,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>26210</v>
       </c>
@@ -1109,7 +1116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>26042</v>
       </c>
@@ -1120,7 +1127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>34556</v>
       </c>
@@ -1131,7 +1138,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>33753</v>
       </c>
@@ -1142,7 +1149,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>32008</v>
       </c>
@@ -1153,7 +1160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>31007</v>
       </c>
@@ -1164,7 +1171,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>26174</v>
       </c>
@@ -1175,7 +1182,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>25330</v>
       </c>
@@ -1186,7 +1193,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>34871</v>
       </c>
@@ -1197,7 +1204,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>26781</v>
       </c>
@@ -1208,7 +1215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>25310</v>
       </c>
@@ -1219,7 +1226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>34296</v>
       </c>
@@ -1230,7 +1237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>32803</v>
       </c>
@@ -1241,7 +1248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>31077</v>
       </c>
@@ -1252,7 +1259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>32672</v>
       </c>
@@ -1263,7 +1270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>33806</v>
       </c>
@@ -1274,7 +1281,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>26609</v>
       </c>
@@ -1285,7 +1292,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>26336</v>
       </c>
@@ -1297,6 +1304,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C81" xr:uid="{0DE483CA-FC21-4D49-9D12-BE057BED5155}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="32473"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;KFF0000 Classificação: Restrito&amp;1#_x000D_</oddHeader>
